--- a/Minería de datos/Practica 4/eve.xlsx
+++ b/Minería de datos/Practica 4/eve.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ranfery\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Practica 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BDB0F513-DFD5-4EDA-8748-1209DAD30C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53E9A8F-5A8E-41CB-86CB-FCA1274F8A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E287BC9-8D66-4019-BF8D-4B9C472C75F6}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7E287BC9-8D66-4019-BF8D-4B9C472C75F6}"/>
   </bookViews>
   <sheets>
     <sheet name="eve" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="53">
   <si>
     <t>Make</t>
   </si>
@@ -149,6 +162,36 @@
   </si>
   <si>
     <t>Entropía del árbol:</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>MT:TESLA-E</t>
+  </si>
+  <si>
+    <t>MT:TESLA-B</t>
+  </si>
+  <si>
+    <t>MT:TESLA-P</t>
+  </si>
+  <si>
+    <t>MT:NISSAN-E</t>
+  </si>
+  <si>
+    <t>MT:NISSAN-B</t>
+  </si>
+  <si>
+    <t>MT:NISSAN-P</t>
+  </si>
+  <si>
+    <t>M:CADILLAC</t>
+  </si>
+  <si>
+    <t>M:FORD</t>
+  </si>
+  <si>
+    <t>M:HUNDAI</t>
   </si>
 </sst>
 </file>
@@ -156,7 +199,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -294,7 +337,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,12 +520,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,12 +684,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1031,6 +1066,8 @@
   <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
     <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
@@ -1089,13 +1126,6 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1113,7 +1143,6 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="3"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
@@ -1137,7 +1166,6 @@
       <c r="M6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="3"/>
       <c r="O6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1157,17 +1185,17 @@
         <v>30</v>
       </c>
       <c r="K7" s="1">
-        <v>6</v>
+        <f>COUNTIF(A2:A101, "TESLA")</f>
+        <v>30</v>
       </c>
       <c r="L7" s="1">
         <f>K7 /$K$16</f>
-        <v>0.31578947368421051</v>
+        <v>30</v>
       </c>
       <c r="M7" s="2">
         <f>-LOG10(L7) * L7</f>
-        <v>0.15808495281132168</v>
-      </c>
-      <c r="N7" s="3"/>
+        <v>-44.313637641589871</v>
+      </c>
       <c r="O7" s="1">
         <v>0.85066438927136601</v>
       </c>
@@ -1187,19 +1215,17 @@
         <v>31</v>
       </c>
       <c r="K8" s="1">
-        <v>3</v>
+        <f>COUNTIF(A3:A102, "NISSAN")</f>
+        <v>13</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" ref="L8:L15" si="0">K8 /$K$16</f>
-        <v>0.15789473684210525</v>
+        <v>13</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" ref="M8:M15" si="1">-LOG10(L8) * L8</f>
-        <v>0.12657352835260524</v>
-      </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+        <v>-14.481263579988877</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1218,19 +1244,17 @@
         <v>32</v>
       </c>
       <c r="K9" s="1">
-        <v>2</v>
+        <f>COUNTIF(A4:A103, "JEEP")</f>
+        <v>4</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>0.10526315789473684</v>
+        <v>4</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="1"/>
-        <v>0.10291827424093135</v>
-      </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+        <v>-2.4082399653118496</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1249,19 +1273,17 @@
         <v>33</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <f>COUNTIF(A5:A104, "AUDI")</f>
+        <v>4</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="1"/>
-        <v>6.7302821102780477E-2</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+        <v>-2.4082399653118496</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1280,19 +1302,17 @@
         <v>34</v>
       </c>
       <c r="K11" s="1">
-        <v>3</v>
+        <f>COUNTIF(A6:A105, "VOLVO")</f>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="0"/>
-        <v>0.15789473684210525</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2">
         <f t="shared" si="1"/>
-        <v>0.12657352835260524</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+        <v>-4.6689075023018614</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1311,19 +1331,17 @@
         <v>35</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <f>COUNTIF(A7:A106, "CHEVROLET")</f>
+        <v>5</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2">
         <f t="shared" si="1"/>
-        <v>6.7302821102780477E-2</v>
-      </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+        <v>-3.4948500216800942</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1342,19 +1360,17 @@
         <v>36</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <f>COUNTIF(A8:A107, "FIAT")</f>
+        <v>2</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2">
         <f t="shared" si="1"/>
-        <v>6.7302821102780477E-2</v>
-      </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+        <v>-0.6020599913279624</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1373,19 +1389,17 @@
         <v>37</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <f>COUNTIF(A9:A108, "KIA")</f>
+        <v>13</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>13</v>
       </c>
       <c r="M14" s="2">
         <f t="shared" si="1"/>
-        <v>6.7302821102780477E-2</v>
-      </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+        <v>-14.481263579988877</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1401,19 +1415,17 @@
         <v>38</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <f>COUNTIF(A10:A109, "BMW")</f>
+        <v>16</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <v>16</v>
       </c>
       <c r="M15" s="2">
         <f t="shared" si="1"/>
-        <v>6.7302821102780477E-2</v>
-      </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+        <v>-19.265919722494797</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1425,24 +1437,23 @@
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="4">
-        <f>SUM(K7:K15)</f>
-        <v>19</v>
-      </c>
-      <c r="L16" s="4">
-        <f>SUM(L7:L15)</f>
-        <v>0.99999999999999978</v>
-      </c>
-      <c r="M16" s="4">
-        <f>SUM(M7:M15)</f>
-        <v>0.85066438927136601</v>
-      </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="1">
+        <f>COUNTIF(A11:A110, "CADILLAC")</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" ref="L16" si="2">K16 /$K$16</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" ref="M16" si="3">-LOG10(L16) * L16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1452,8 +1463,15 @@
       <c r="C17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" ref="K17:K18" si="4">COUNTIF(A12:A111, "CADILLAC")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1463,8 +1481,15 @@
       <c r="C18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1474,8 +1499,12 @@
       <c r="C19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <f>SUM(K7:K18)</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1485,8 +1514,11 @@
       <c r="C20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1497,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1507,8 +1539,14 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1518,8 +1556,14 @@
       <c r="C23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1529,8 +1573,14 @@
       <c r="C24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1590,14 @@
       <c r="C25" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1551,8 +1607,11 @@
       <c r="C26" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -1562,8 +1621,11 @@
       <c r="C27" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1574,7 +1636,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1585,7 +1647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1596,7 +1658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -1607,7 +1669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
